--- a/Output/arima_model_all_weekly_output.xlsx
+++ b/Output/arima_model_all_weekly_output.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -8168,7 +8168,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8448,7 +8448,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -11493,7 +11493,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11668,7 +11668,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11703,7 +11703,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -11808,7 +11808,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -19105,7 +19105,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.8871 (1.6853, 2.0890)</t>
+          <t>1.8871
+ (1.6853, 2.0890)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -19115,7 +19116,8 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.0047 (-0.0223, 0.0129)</t>
+          <t>-0.0047
+ (-0.0223, 0.0129)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -19125,7 +19127,8 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.2271 (0.0148, 0.4394)</t>
+          <t>0.2271
+ (0.0148, 0.4394)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -19135,7 +19138,8 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0035 (-0.0150, 0.0220)</t>
+          <t>0.0035
+ (-0.0150, 0.0220)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -19145,7 +19149,8 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1454 (-0.1202, 0.4110)</t>
+          <t>0.1454
+ (-0.1202, 0.4110)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -19155,7 +19160,8 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>-0.0011 (-0.0147, 0.0125)</t>
+          <t>-0.0011
+ (-0.0147, 0.0125)</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -19177,7 +19183,8 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.0114 (1.6572, 2.3656)</t>
+          <t>2.0114
+ (1.6572, 2.3656)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -19187,7 +19194,8 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0029 (-0.0096, 0.0154)</t>
+          <t>0.0029
+ (-0.0096, 0.0154)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -19197,7 +19205,8 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.4153 (-0.0340, 0.8647)</t>
+          <t>0.4153
+ (-0.0340, 0.8647)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -19207,7 +19216,8 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.0032 (-0.0120, 0.0185)</t>
+          <t>0.0032
+ (-0.0120, 0.0185)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -19217,7 +19227,8 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.1921 (-0.2465, 0.6308)</t>
+          <t>0.1921
+ (-0.2465, 0.6308)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -19227,7 +19238,8 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-0.0140 (-0.0286, 0.0007)</t>
+          <t>-0.0140
+ (-0.0286, 0.0007)</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -19249,7 +19261,8 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>74.2952 (72.9282, 75.6622)</t>
+          <t>74.2952
+ (72.9282, 75.6622)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -19259,7 +19272,8 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0322 (0.0094, 0.0550)</t>
+          <t>0.0322
+ (0.0094, 0.0550)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -19269,7 +19283,8 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.4716 (-4.2736, -0.6695)</t>
+          <t>-2.4716
+ (-4.2736, -0.6695)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -19279,7 +19294,8 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.0241 (-0.0642, 0.0160)</t>
+          <t>-0.0241
+ (-0.0642, 0.0160)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -19289,7 +19305,8 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.2190 (-2.0137, 1.5757)</t>
+          <t>-0.2190
+ (-2.0137, 1.5757)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -19299,7 +19316,8 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0103 (-0.0297, 0.0503)</t>
+          <t>0.0103
+ (-0.0297, 0.0503)</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -19321,7 +19339,8 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>21.7769 (20.5919, 22.9620)</t>
+          <t>21.7769
+ (20.5919, 22.9620)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -19331,7 +19350,8 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.0295 (-0.0500, -0.0090)</t>
+          <t>-0.0295
+ (-0.0500, -0.0090)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -19341,7 +19361,8 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1.6733 (0.1210, 3.2255)</t>
+          <t>1.6733
+ (0.1210, 3.2255)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -19351,7 +19372,8 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0180 (-0.0171, 0.0531)</t>
+          <t>0.0180
+ (-0.0171, 0.0531)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -19361,7 +19383,8 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>-0.1601 (-1.6936, 1.3734)</t>
+          <t>-0.1601
+ (-1.6936, 1.3734)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -19371,7 +19394,8 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.0030 (-0.0320, 0.0381)</t>
+          <t>0.0030
+ (-0.0320, 0.0381)</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -19393,7 +19417,8 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.2318 (0.1436, 0.3200)</t>
+          <t>0.2318
+ (0.1436, 0.3200)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -19403,7 +19428,8 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.0013 (-0.0078, 0.0052)</t>
+          <t>-0.0013
+ (-0.0078, 0.0052)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -19413,7 +19439,8 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.0576 (-0.1331, 0.0180)</t>
+          <t>-0.0576
+ (-0.1331, 0.0180)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -19423,7 +19450,8 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.0036 (-0.0063, 0.0135)</t>
+          <t>0.0036
+ (-0.0063, 0.0135)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -19433,7 +19461,8 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0311 (-0.0441, 0.1063)</t>
+          <t>0.0311
+ (-0.0441, 0.1063)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -19443,7 +19472,8 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.0017 (-0.0129, 0.0095)</t>
+          <t>-0.0017
+ (-0.0129, 0.0095)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -19465,7 +19495,8 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.4137 (4.0835, 4.7439)</t>
+          <t>4.4137
+ (4.0835, 4.7439)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -19475,7 +19506,8 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0127 (0.0005, 0.0250)</t>
+          <t>0.0127
+ (0.0005, 0.0250)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -19485,7 +19517,8 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.1198 (-1.6020, -0.6376)</t>
+          <t>-1.1198
+ (-1.6020, -0.6376)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -19495,7 +19528,8 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0168 (0.0021, 0.0315)</t>
+          <t>0.0168
+ (0.0021, 0.0315)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -19505,7 +19539,8 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.0711 (-0.4048, 0.5469)</t>
+          <t>0.0711
+ (-0.4048, 0.5469)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -19515,7 +19550,8 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-0.0387 (-0.0532, -0.0242)</t>
+          <t>-0.0387
+ (-0.0532, -0.0242)</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -19537,7 +19573,8 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.5930 (3.9005, 5.2856)</t>
+          <t>4.5930
+ (3.9005, 5.2856)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -19547,7 +19584,8 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0009 (-0.0142, 0.0160)</t>
+          <t>0.0009
+ (-0.0142, 0.0160)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -19557,7 +19595,8 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-0.6100 (-1.2549, 0.0349)</t>
+          <t>-0.6100
+ (-1.2549, 0.0349)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -19567,7 +19606,8 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0038 (-0.0188, 0.0265)</t>
+          <t>0.0038
+ (-0.0188, 0.0265)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -19577,7 +19617,8 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-0.0686 (-0.7062, 0.5691)</t>
+          <t>-0.0686
+ (-0.7062, 0.5691)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -19587,7 +19628,8 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.0004 (-0.0223, 0.0215)</t>
+          <t>-0.0004
+ (-0.0223, 0.0215)</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -19609,7 +19651,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5.5900 (5.0403, 6.1396)</t>
+          <t>5.5900
+ (5.0403, 6.1396)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -19619,7 +19662,8 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.0093 (-0.0242, 0.0055)</t>
+          <t>-0.0093
+ (-0.0242, 0.0055)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -19629,7 +19673,8 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.4360 (-0.1245, 0.9964)</t>
+          <t>0.4360
+ (-0.1245, 0.9964)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -19639,7 +19684,8 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.0054 (-0.0149, 0.0256)</t>
+          <t>0.0054
+ (-0.0149, 0.0256)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -19649,7 +19695,8 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.1038 (-0.4608, 0.6685)</t>
+          <t>0.1038
+ (-0.4608, 0.6685)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -19659,7 +19706,8 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.0282 (0.0091, 0.0472)</t>
+          <t>0.0282
+ (0.0091, 0.0472)</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -19681,7 +19729,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.2856 (3.7198, 4.8513)</t>
+          <t>4.2856
+ (3.7198, 4.8513)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -19691,7 +19740,8 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.0104 (-0.0244, 0.0035)</t>
+          <t>-0.0104
+ (-0.0244, 0.0035)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -19701,7 +19751,8 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1.3978 (0.5987, 2.1968)</t>
+          <t>1.3978
+ (0.5987, 2.1968)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -19711,7 +19762,8 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0003 (-0.0194, 0.0200)</t>
+          <t>0.0003
+ (-0.0194, 0.0200)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -19721,7 +19773,8 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.1417 (-0.6418, 0.9251)</t>
+          <t>0.1417
+ (-0.6418, 0.9251)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -19731,7 +19784,8 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.0091 (-0.0104, 0.0285)</t>
+          <t>0.0091
+ (-0.0104, 0.0285)</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -19753,7 +19807,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7.4047 (6.0156, 8.7937)</t>
+          <t>7.4047
+ (6.0156, 8.7937)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -19763,7 +19818,8 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0398 (0.0171, 0.0624)</t>
+          <t>0.0398
+ (0.0171, 0.0624)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -19773,7 +19829,8 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.0425 (-2.5413, 0.4563)</t>
+          <t>-1.0425
+ (-2.5413, 0.4563)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -19783,7 +19840,8 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.0229 (-0.0631, 0.0174)</t>
+          <t>-0.0229
+ (-0.0631, 0.0174)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -19793,7 +19851,8 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-0.5195 (-2.0017, 0.9627)</t>
+          <t>-0.5195
+ (-2.0017, 0.9627)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -19803,7 +19862,8 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-0.0161 (-0.0561, 0.0239)</t>
+          <t>-0.0161
+ (-0.0561, 0.0239)</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -19825,7 +19885,8 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.5890 (0.5297, 0.6484)</t>
+          <t>0.5890
+ (0.5297, 0.6484)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -19835,7 +19896,8 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-0.0029 (-0.0154, 0.0096)</t>
+          <t>-0.0029
+ (-0.0154, 0.0096)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -19845,7 +19907,8 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.1356 (0.0497, 0.2214)</t>
+          <t>0.1356
+ (0.0497, 0.2214)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -19855,7 +19918,8 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0038 (-0.0081, 0.0157)</t>
+          <t>0.0038
+ (-0.0081, 0.0157)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -19865,7 +19929,8 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.1553 (0.0627, 0.2479)</t>
+          <t>0.1553
+ (0.0627, 0.2479)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -19875,7 +19940,8 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-0.0036 (-0.0148, 0.0075)</t>
+          <t>-0.0036
+ (-0.0148, 0.0075)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -19892,12 +19958,13 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Food Colour/Flavour and Baking Additivies</t>
+          <t>Food Colour/Flavour and Baking Additives</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.2464 (1.0253, 1.4676)</t>
+          <t>1.2464
+ (1.0253, 1.4676)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -19907,7 +19974,8 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-0.0039 (-0.0155, 0.0078)</t>
+          <t>-0.0039
+ (-0.0155, 0.0078)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -19917,7 +19985,8 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.4919 (0.1639, 0.8200)</t>
+          <t>0.4919
+ (0.1639, 0.8200)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -19927,7 +19996,8 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-0.0017 (-0.0145, 0.0111)</t>
+          <t>-0.0017
+ (-0.0145, 0.0111)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -19937,7 +20007,8 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.0993 (-0.2200, 0.4185)</t>
+          <t>0.0993
+ (-0.2200, 0.4185)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -19947,7 +20018,8 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.0030 (-0.0097, 0.0156)</t>
+          <t>0.0030
+ (-0.0097, 0.0156)</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -19969,7 +20041,8 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.6948 (0.4355, 0.9541)</t>
+          <t>0.6948
+ (0.4355, 0.9541)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -19979,7 +20052,8 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.0019 (-0.0102, 0.0139)</t>
+          <t>0.0019
+ (-0.0102, 0.0139)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -19989,7 +20063,8 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-0.1564 (-0.4527, 0.1400)</t>
+          <t>-0.1564
+ (-0.4527, 0.1400)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -19999,7 +20074,8 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.0060 (-0.0077, 0.0196)</t>
+          <t>0.0060
+ (-0.0077, 0.0196)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -20009,7 +20085,8 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-0.1858 (-0.4863, 0.1147)</t>
+          <t>-0.1858
+ (-0.4863, 0.1147)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -20019,7 +20096,8 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-0.0134 (-0.0263, -0.0005)</t>
+          <t>-0.0134
+ (-0.0263, -0.0005)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -20041,7 +20119,8 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.2801 (0.2350, 0.3252)</t>
+          <t>0.2801
+ (0.2350, 0.3252)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -20051,7 +20130,8 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-0.0003 (-0.0066, 0.0061)</t>
+          <t>-0.0003
+ (-0.0066, 0.0061)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -20061,7 +20141,8 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.0590 (-0.0040, 0.1220)</t>
+          <t>0.0590
+ (-0.0040, 0.1220)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -20071,7 +20152,8 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.0004 (-0.0089, 0.0098)</t>
+          <t>0.0004
+ (-0.0089, 0.0098)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -20081,7 +20163,8 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.0115 (-0.0491, 0.0722)</t>
+          <t>0.0115
+ (-0.0491, 0.0722)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -20091,7 +20174,8 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-0.0004 (-0.0111, 0.0104)</t>
+          <t>-0.0004
+ (-0.0111, 0.0104)</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -20113,7 +20197,8 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.7358 (1.5829, 1.8887)</t>
+          <t>1.7358
+ (1.5829, 1.8887)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -20123,7 +20208,8 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-0.0075 (-0.0195, 0.0045)</t>
+          <t>-0.0075
+ (-0.0195, 0.0045)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -20133,7 +20219,8 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.5407 (0.3303, 0.7511)</t>
+          <t>0.5407
+ (0.3303, 0.7511)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -20143,7 +20230,8 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0081 (-0.0042, 0.0204)</t>
+          <t>0.0081
+ (-0.0042, 0.0204)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -20153,7 +20241,8 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.0624 (-0.1507, 0.2756)</t>
+          <t>0.0624
+ (-0.1507, 0.2756)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -20163,7 +20252,8 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-0.0002 (-0.0119, 0.0115)</t>
+          <t>-0.0002
+ (-0.0119, 0.0115)</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -20185,7 +20275,8 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22.1542 (20.8233, 23.4851)</t>
+          <t>22.1542
+ (20.8233, 23.4851)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -20195,7 +20286,8 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-0.0245 (-0.0468, -0.0022)</t>
+          <t>-0.0245
+ (-0.0468, -0.0022)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -20205,7 +20297,8 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>1.1238 (-0.5887, 2.8363)</t>
+          <t>1.1238
+ (-0.5887, 2.8363)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -20215,7 +20308,8 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.0034 (-0.0352, 0.0419)</t>
+          <t>0.0034
+ (-0.0352, 0.0419)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -20225,7 +20319,8 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.2070 (-1.4201, 1.8341)</t>
+          <t>0.2070
+ (-1.4201, 1.8341)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -20235,7 +20330,8 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.0001 (-0.0387, 0.0388)</t>
+          <t>0.0001
+ (-0.0387, 0.0388)</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -20257,7 +20353,8 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.5452 (0.4303, 0.6602)</t>
+          <t>0.5452
+ (0.4303, 0.6602)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -20267,7 +20364,8 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.0009 (-0.0150, 0.0168)</t>
+          <t>0.0009
+ (-0.0150, 0.0168)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -20277,7 +20375,8 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.1458 (-0.0016, 0.2932)</t>
+          <t>0.1458
+ (-0.0016, 0.2932)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -20287,7 +20386,8 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.0044 (-0.0096, 0.0184)</t>
+          <t>0.0044
+ (-0.0096, 0.0184)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -20297,7 +20397,8 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.0731 (-0.1290, 0.2752)</t>
+          <t>0.0731
+ (-0.1290, 0.2752)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -20307,7 +20408,8 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-0.0071 (-0.0183, 0.0042)</t>
+          <t>-0.0071
+ (-0.0183, 0.0042)</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -20329,7 +20431,8 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.3243 (1.2207, 1.4279)</t>
+          <t>1.3243
+ (1.2207, 1.4279)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -20339,7 +20442,8 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-0.0059 (-0.0121, 0.0003)</t>
+          <t>-0.0059
+ (-0.0121, 0.0003)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -20349,7 +20453,8 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.0244 (-0.0934, 0.1423)</t>
+          <t>0.0244
+ (-0.0934, 0.1423)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -20359,7 +20464,8 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.0074 (-0.0004, 0.0151)</t>
+          <t>0.0074
+ (-0.0004, 0.0151)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -20369,7 +20475,8 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.0624 (-0.0275, 0.1523)</t>
+          <t>0.0624
+ (-0.0275, 0.1523)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -20379,7 +20486,8 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-0.0017 (-0.0127, 0.0092)</t>
+          <t>-0.0017
+ (-0.0127, 0.0092)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -20401,7 +20509,8 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4.0798 (3.5662, 4.5933)</t>
+          <t>4.0798
+ (3.5662, 4.5933)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -20411,7 +20520,8 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0038 (-0.0097, 0.0174)</t>
+          <t>0.0038
+ (-0.0097, 0.0174)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -20421,7 +20531,8 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.5578 (-0.0992, 1.2149)</t>
+          <t>0.5578
+ (-0.0992, 1.2149)</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -20431,7 +20542,8 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0095 (-0.0090, 0.0280)</t>
+          <t>0.0095
+ (-0.0090, 0.0280)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -20441,7 +20553,8 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-0.2288 (-0.8779, 0.4203)</t>
+          <t>-0.2288
+ (-0.8779, 0.4203)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -20451,7 +20564,8 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-0.0234 (-0.0413, -0.0055)</t>
+          <t>-0.0234
+ (-0.0413, -0.0055)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -20473,7 +20587,8 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.7850 (1.6409, 1.9290)</t>
+          <t>1.7850
+ (1.6409, 1.9290)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -20483,7 +20598,8 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-0.0002 (-0.0122, 0.0117)</t>
+          <t>-0.0002
+ (-0.0122, 0.0117)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -20493,7 +20609,8 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.1368 (-0.0611, 0.3347)</t>
+          <t>0.1368
+ (-0.0611, 0.3347)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -20503,7 +20620,8 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-0.0021 (-0.0143, 0.0102)</t>
+          <t>-0.0021
+ (-0.0143, 0.0102)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -20513,7 +20631,8 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.0831 (-0.1200, 0.2861)</t>
+          <t>0.0831
+ (-0.1200, 0.2861)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -20523,7 +20642,8 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.0035 (-0.0081, 0.0151)</t>
+          <t>0.0035
+ (-0.0081, 0.0151)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -20540,12 +20660,13 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sweet Snacks/Baked Foods</t>
+          <t>Sweet Snacks/Sweet Baked Foods</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>39.4815 (36.8451, 42.1179)</t>
+          <t>39.4815
+ (36.8451, 42.1179)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -20555,7 +20676,8 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-0.0020 (-0.0409, 0.0369)</t>
+          <t>-0.0020
+ (-0.0409, 0.0369)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -20565,7 +20687,8 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.8355 (-3.6987, 2.0276)</t>
+          <t>-0.8355
+ (-3.6987, 2.0276)</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -20575,7 +20698,8 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-0.0535 (-0.1261, 0.0191)</t>
+          <t>-0.0535
+ (-0.1261, 0.0191)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -20585,7 +20709,8 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.7716 (-1.9264, 3.4696)</t>
+          <t>0.7716
+ (-1.9264, 3.4696)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -20595,7 +20720,8 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.0736 (0.0006, 0.1466)</t>
+          <t>0.0736
+ (0.0006, 0.1466)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -20617,7 +20743,8 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>534.0219 (510.1383, 557.9056)</t>
+          <t>534.0219
+ (510.1383, 557.9056)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -20627,7 +20754,8 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.6265 (0.2796, 0.9734)</t>
+          <t>0.6265
+ (0.2796, 0.9734)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -20637,7 +20765,8 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5.7608 (-25.4839, 37.0055)</t>
+          <t>5.7608
+ (-25.4839, 37.0055)</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -20647,7 +20776,8 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-0.0511 (-0.7256, 0.6235)</t>
+          <t>-0.0511
+ (-0.7256, 0.6235)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -20657,7 +20787,8 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-7.1228 (-38.1618, 23.9162)</t>
+          <t>-7.1228
+ (-38.1618, 23.9162)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -20667,7 +20798,8 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>-0.7579 (-1.4327, -0.0830)</t>
+          <t>-0.7579
+ (-1.4327, -0.0830)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -20689,7 +20821,8 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>39.0686 (37.4957, 40.6416)</t>
+          <t>39.0686
+ (37.4957, 40.6416)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -20699,7 +20832,8 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-0.0091 (-0.0312, 0.0130)</t>
+          <t>-0.0091
+ (-0.0312, 0.0130)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -20709,7 +20843,8 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.7891 (-2.4119, 0.8336)</t>
+          <t>-0.7891
+ (-2.4119, 0.8336)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -20719,7 +20854,8 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.0137 (-0.0298, 0.0572)</t>
+          <t>0.0137
+ (-0.0298, 0.0572)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -20729,7 +20865,8 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.1350 (-1.4775, 1.7475)</t>
+          <t>0.1350
+ (-1.4775, 1.7475)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -20739,7 +20876,8 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-0.0095 (-0.0531, 0.0340)</t>
+          <t>-0.0095
+ (-0.0531, 0.0340)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -20761,7 +20899,8 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>6.2559 (6.1874, 6.3245)</t>
+          <t>6.2559
+ (6.1874, 6.3245)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -20771,7 +20910,8 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-0.0037 (-0.0047, -0.0027)</t>
+          <t>-0.0037
+ (-0.0047, -0.0027)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -20781,7 +20921,8 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.2738 (0.1746, 0.3729)</t>
+          <t>0.2738
+ (0.1746, 0.3729)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -20791,7 +20932,8 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0027 (0.0007, 0.0046)</t>
+          <t>0.0027
+ (0.0007, 0.0046)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -20801,7 +20943,8 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.0677 (-0.0307, 0.1661)</t>
+          <t>0.0677
+ (-0.0307, 0.1661)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -20811,7 +20954,8 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.0015 (-0.0005, 0.0035)</t>
+          <t>0.0015
+ (-0.0005, 0.0035)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -20833,7 +20977,8 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11.4115 (11.0230, 11.8000)</t>
+          <t>11.4115
+ (11.0230, 11.8000)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -20843,7 +20988,8 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.0011 (-0.0045, 0.0067)</t>
+          <t>0.0011
+ (-0.0045, 0.0067)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -20853,7 +20999,8 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.2717 (-0.2074, 0.7507)</t>
+          <t>0.2717
+ (-0.2074, 0.7507)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -20863,7 +21010,8 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0098 (-0.0010, 0.0206)</t>
+          <t>0.0098
+ (-0.0010, 0.0206)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -20873,7 +21021,8 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.0539 (-0.4092, 0.5169)</t>
+          <t>0.0539
+ (-0.4092, 0.5169)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -20883,7 +21032,8 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>-0.0200 (-0.0309, -0.0091)</t>
+          <t>-0.0200
+ (-0.0309, -0.0091)</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -20905,7 +21055,8 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>43.2752 (42.1291, 44.4212)</t>
+          <t>43.2752
+ (42.1291, 44.4212)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -20915,7 +21066,8 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.0121 (-0.0042, 0.0284)</t>
+          <t>0.0121
+ (-0.0042, 0.0284)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -20925,7 +21077,8 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-0.4061 (-1.7169, 0.9047)</t>
+          <t>-0.4061
+ (-1.7169, 0.9047)</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -20935,7 +21088,8 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-0.0134 (-0.0453, 0.0184)</t>
+          <t>-0.0134
+ (-0.0453, 0.0184)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -20945,7 +21099,8 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-0.1434 (-1.4542, 1.1673)</t>
+          <t>-0.1434
+ (-1.4542, 1.1673)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -20955,7 +21110,8 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.0148 (-0.0169, 0.0466)</t>
+          <t>0.0148
+ (-0.0169, 0.0466)</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -20977,7 +21133,8 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4.0969 (3.8900, 4.3038)</t>
+          <t>4.0969
+ (3.8900, 4.3038)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -20987,7 +21144,8 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-0.0030 (-0.0060, 0.0001)</t>
+          <t>-0.0030
+ (-0.0060, 0.0001)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -20997,7 +21155,8 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.4676 (0.1754, 0.7599)</t>
+          <t>0.4676
+ (0.1754, 0.7599)</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -21007,7 +21166,8 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.0016 (-0.0043, 0.0075)</t>
+          <t>0.0016
+ (-0.0043, 0.0075)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -21017,7 +21177,8 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>0.0185 (-0.2651, 0.3021)</t>
+          <t>0.0185
+ (-0.2651, 0.3021)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -21027,7 +21188,8 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-0.0003 (-0.0062, 0.0056)</t>
+          <t>-0.0003
+ (-0.0062, 0.0056)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -21049,7 +21211,8 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20.4379 (18.9068, 21.9690)</t>
+          <t>20.4379
+ (18.9068, 21.9690)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -21059,7 +21222,8 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0.0148 (-0.0068, 0.0363)</t>
+          <t>0.0148
+ (-0.0068, 0.0363)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -21069,7 +21233,8 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>1.0348 (-0.5803, 2.6498)</t>
+          <t>1.0348
+ (-0.5803, 2.6498)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -21079,7 +21244,8 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-0.0223 (-0.0648, 0.0203)</t>
+          <t>-0.0223
+ (-0.0648, 0.0203)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -21089,7 +21255,8 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1.1801 (-0.4984, 2.8587)</t>
+          <t>1.1801
+ (-0.4984, 2.8587)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -21099,7 +21266,8 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-0.0044 (-0.0468, 0.0381)</t>
+          <t>-0.0044
+ (-0.0468, 0.0381)</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -21121,7 +21289,8 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>96.2366 (92.3680, 100.1053)</t>
+          <t>96.2366
+ (92.3680, 100.1053)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -21131,7 +21300,8 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-0.0096 (-0.0667, 0.0475)</t>
+          <t>-0.0096
+ (-0.0667, 0.0475)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -21141,7 +21311,8 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>8.8285 (3.3571, 14.3000)</t>
+          <t>8.8285
+ (3.3571, 14.3000)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -21151,7 +21322,8 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-0.0881 (-0.1974, 0.0211)</t>
+          <t>-0.0881
+ (-0.1974, 0.0211)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -21161,7 +21333,8 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>0.8640 (-4.3165, 6.0445)</t>
+          <t>0.8640
+ (-4.3165, 6.0445)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -21171,7 +21344,8 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>0.0513 (-0.0593, 0.1618)</t>
+          <t>0.0513
+ (-0.0593, 0.1618)</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -21193,7 +21367,8 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2.2175 (2.1383, 2.2966)</t>
+          <t>2.2175
+ (2.1383, 2.2966)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -21203,7 +21378,8 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-0.0020 (-0.0031, -0.0008)</t>
+          <t>-0.0020
+ (-0.0031, -0.0008)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -21213,7 +21389,8 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.1635 (0.0478, 0.2792)</t>
+          <t>0.1635
+ (0.0478, 0.2792)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -21223,7 +21400,8 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.0010 (-0.0012, 0.0033)</t>
+          <t>0.0010
+ (-0.0012, 0.0033)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -21233,7 +21411,8 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.0415 (-0.0735, 0.1564)</t>
+          <t>0.0415
+ (-0.0735, 0.1564)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -21243,7 +21422,8 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.0009 (-0.0014, 0.0032)</t>
+          <t>0.0009
+ (-0.0014, 0.0032)</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -21265,7 +21445,8 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>34.9134 (33.7241, 36.1028)</t>
+          <t>34.9134
+ (33.7241, 36.1028)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -21275,7 +21456,8 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-0.0213 (-0.0386, -0.0040)</t>
+          <t>-0.0213
+ (-0.0386, -0.0040)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -21285,7 +21467,8 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3.1270 (1.5434, 4.7106)</t>
+          <t>3.1270
+ (1.5434, 4.7106)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -21295,7 +21478,8 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.0092 (-0.0246, 0.0430)</t>
+          <t>0.0092
+ (-0.0246, 0.0430)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -21305,7 +21489,8 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.4964 (-1.0575, 2.0503)</t>
+          <t>0.4964
+ (-1.0575, 2.0503)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -21315,7 +21500,8 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.0068 (-0.0271, 0.0407)</t>
+          <t>0.0068
+ (-0.0271, 0.0407)</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -21337,7 +21523,8 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>135.7153 (130.8427, 140.5879)</t>
+          <t>135.7153
+ (130.8427, 140.5879)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -21347,7 +21534,8 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>-0.0004 (-0.0721, 0.0714)</t>
+          <t>-0.0004
+ (-0.0721, 0.0714)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -21357,7 +21545,8 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>11.1576 (4.2947, 18.0206)</t>
+          <t>11.1576
+ (4.2947, 18.0206)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -21367,7 +21556,8 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-0.0786 (-0.2173, 0.0601)</t>
+          <t>-0.0786
+ (-0.2173, 0.0601)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -21377,7 +21567,8 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2.8817 (-3.8175, 9.5808)</t>
+          <t>2.8817
+ (-3.8175, 9.5808)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -21387,7 +21578,8 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.0088 (-0.1307, 0.1482)</t>
+          <t>0.0088
+ (-0.1307, 0.1482)</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -21409,7 +21601,8 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>306.9143 (298.5621, 315.2665)</t>
+          <t>306.9143
+ (298.5621, 315.2665)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -21419,7 +21612,8 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>-0.1714 (-0.2950, -0.0478)</t>
+          <t>-0.1714
+ (-0.2950, -0.0478)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -21429,7 +21623,8 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>28.3732 (16.3004, 40.4459)</t>
+          <t>28.3732
+ (16.3004, 40.4459)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -21439,7 +21634,8 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.0538 (-0.1852, 0.2928)</t>
+          <t>0.0538
+ (-0.1852, 0.2928)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -21449,7 +21645,8 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.2298 (-11.5398, 11.9994)</t>
+          <t>0.2298
+ (-11.5398, 11.9994)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -21459,7 +21656,8 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>-0.0706 (-0.3107, 0.1696)</t>
+          <t>-0.0706
+ (-0.3107, 0.1696)</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -21481,7 +21679,8 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>338.1077 (316.5789, 359.6365)</t>
+          <t>338.1077
+ (316.5789, 359.6365)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -21491,7 +21690,8 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>-0.5714 (-0.8871, -0.2556)</t>
+          <t>-0.5714
+ (-0.8871, -0.2556)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -21501,7 +21701,8 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>55.1169 (24.2455, 85.9882)</t>
+          <t>55.1169
+ (24.2455, 85.9882)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -21511,7 +21712,8 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-0.2410 (-0.8786, 0.3965)</t>
+          <t>-0.2410
+ (-0.8786, 0.3965)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -21521,7 +21723,8 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>19.9590 (-13.0832, 53.0013)</t>
+          <t>19.9590
+ (-13.0832, 53.0013)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -21531,7 +21734,8 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.7997 (0.1737, 1.4257)</t>
+          <t>0.7997
+ (0.1737, 1.4257)</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -21553,7 +21757,8 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.7540 (0.7378, 0.7701)</t>
+          <t>0.7540
+ (0.7378, 0.7701)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -21563,7 +21768,8 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-0.0001 (-0.0004, 0.0002)</t>
+          <t>-0.0001
+ (-0.0004, 0.0002)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -21573,7 +21779,8 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.0421 (0.0187, 0.0654)</t>
+          <t>0.0421
+ (0.0187, 0.0654)</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -21583,7 +21790,8 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.0001 (-0.0004, 0.0005)</t>
+          <t>0.0001
+ (-0.0004, 0.0005)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -21593,7 +21801,8 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.0132 (-0.0094, 0.0357)</t>
+          <t>0.0132
+ (-0.0094, 0.0357)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -21603,7 +21812,8 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.0000 (-0.0005, 0.0004)</t>
+          <t>0.0000
+ (-0.0005, 0.0004)</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -21625,7 +21835,8 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6.6216 (6.5160, 6.7271)</t>
+          <t>6.6216
+ (6.5160, 6.7271)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -21635,7 +21846,8 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-0.0044 (-0.0060, -0.0029)</t>
+          <t>-0.0044
+ (-0.0060, -0.0029)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -21645,7 +21857,8 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.1951 (0.0415, 0.3486)</t>
+          <t>0.1951
+ (0.0415, 0.3486)</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -21655,7 +21868,8 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.0059 (0.0029, 0.0090)</t>
+          <t>0.0059
+ (0.0029, 0.0090)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -21665,7 +21879,8 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.1900 (0.0365, 0.3435)</t>
+          <t>0.1900
+ (0.0365, 0.3435)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -21675,7 +21890,8 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>-0.0001 (-0.0032, 0.0029)</t>
+          <t>-0.0001
+ (-0.0032, 0.0029)</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -21697,7 +21913,8 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>163.7523 (152.4545, 175.0500)</t>
+          <t>163.7523
+ (152.4545, 175.0500)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -21707,7 +21924,8 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-0.4306 (-0.5944, -0.2668)</t>
+          <t>-0.4306
+ (-0.5944, -0.2668)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -21717,7 +21935,8 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>17.1901 (3.3823, 30.9978)</t>
+          <t>17.1901
+ (3.3823, 30.9978)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -21727,7 +21946,8 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.2392 (-0.0654, 0.5439)</t>
+          <t>0.2392
+ (-0.0654, 0.5439)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -21737,7 +21957,8 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4.0687 (-9.3636, 17.5011)</t>
+          <t>4.0687
+ (-9.3636, 17.5011)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -21747,7 +21968,8 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.1548 (-0.1409, 0.4505)</t>
+          <t>0.1548
+ (-0.1409, 0.4505)</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -21769,7 +21991,8 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.1827 (0.1801, 0.1853)</t>
+          <t>0.1827
+ (0.1801, 0.1853)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -21779,7 +22002,8 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>-0.0002 (-0.0003, 0.0000)</t>
+          <t>-0.0002
+ (-0.0003, 0.0000)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -21789,7 +22013,8 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.0036 (-0.0001, 0.0072)</t>
+          <t>0.0036
+ (-0.0001, 0.0072)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -21799,7 +22024,8 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.0002 (0.0000, 0.0003)</t>
+          <t>0.0002
+ (0.0000, 0.0003)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -21809,7 +22035,8 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.0016 (-0.0021, 0.0053)</t>
+          <t>0.0016
+ (-0.0021, 0.0053)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -21819,7 +22046,8 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.0001 (-0.0001, 0.0002)</t>
+          <t>0.0001
+ (-0.0001, 0.0002)</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -21841,7 +22069,8 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.2975 (0.2369, 0.3581)</t>
+          <t>0.2975
+ (0.2369, 0.3581)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -21851,7 +22080,8 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.0003 (-0.0006, 0.0012)</t>
+          <t>0.0003
+ (-0.0006, 0.0012)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -21861,7 +22091,8 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.1516 (-0.2383, -0.0649)</t>
+          <t>-0.1516
+ (-0.2383, -0.0649)</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -21871,7 +22102,8 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.0003 (-0.0014, 0.0020)</t>
+          <t>0.0003
+ (-0.0014, 0.0020)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -21881,7 +22113,8 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>-0.0159 (-0.0978, 0.0661)</t>
+          <t>-0.0159
+ (-0.0978, 0.0661)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -21891,7 +22124,8 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>-0.0002 (-0.0020, 0.0015)</t>
+          <t>-0.0002
+ (-0.0020, 0.0015)</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -21913,7 +22147,8 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2.2130 (2.1701, 2.2559)</t>
+          <t>2.2130
+ (2.1701, 2.2559)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -21923,7 +22158,8 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>-0.0007 (-0.0014, -0.0001)</t>
+          <t>-0.0007
+ (-0.0014, -0.0001)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -21933,7 +22169,8 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.0683 (0.0046, 0.1321)</t>
+          <t>0.0683
+ (0.0046, 0.1321)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -21943,7 +22180,8 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.0015 (0.0003, 0.0028)</t>
+          <t>0.0015
+ (0.0003, 0.0028)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -21953,7 +22191,8 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.0150 (-0.0487, 0.0788)</t>
+          <t>0.0150
+ (-0.0487, 0.0788)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -21963,7 +22202,8 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>-0.0002 (-0.0014, 0.0010)</t>
+          <t>-0.0002
+ (-0.0014, 0.0010)</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -21985,7 +22225,8 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>24.4763 (23.2472, 25.7053)</t>
+          <t>24.4763
+ (23.2472, 25.7053)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -21995,7 +22236,8 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-0.0217 (-0.0400, -0.0035)</t>
+          <t>-0.0217
+ (-0.0400, -0.0035)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -22005,7 +22247,8 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2.3982 (0.5971, 4.1993)</t>
+          <t>2.3982
+ (0.5971, 4.1993)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -22015,7 +22258,8 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.0150 (-0.0202, 0.0502)</t>
+          <t>0.0150
+ (-0.0202, 0.0502)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -22025,7 +22269,8 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1.1589 (-0.5998, 2.9176)</t>
+          <t>1.1589
+ (-0.5998, 2.9176)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -22035,7 +22280,8 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-0.0167 (-0.0522, 0.0187)</t>
+          <t>-0.0167
+ (-0.0522, 0.0187)</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -22057,7 +22303,8 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.5562 (0.5371, 0.5754)</t>
+          <t>0.5562
+ (0.5371, 0.5754)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -22067,7 +22314,8 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-0.0003 (-0.0006, 0.0000)</t>
+          <t>-0.0003
+ (-0.0006, 0.0000)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -22077,7 +22325,8 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.0247 (0.0007, 0.0487)</t>
+          <t>0.0247
+ (0.0007, 0.0487)</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -22087,7 +22336,8 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.0005 (-0.0001, 0.0010)</t>
+          <t>0.0005
+ (-0.0001, 0.0010)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -22097,7 +22347,8 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.0066 (-0.0186, 0.0319)</t>
+          <t>0.0066
+ (-0.0186, 0.0319)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -22107,7 +22358,8 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-0.0007 (-0.0012, -0.0001)</t>
+          <t>-0.0007
+ (-0.0012, -0.0001)</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -22129,7 +22381,8 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>6.6657 (6.3916, 6.9398)</t>
+          <t>6.6657
+ (6.3916, 6.9398)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -22139,7 +22392,8 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0061 (0.0022, 0.0101)</t>
+          <t>0.0061
+ (0.0022, 0.0101)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -22149,7 +22403,8 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.2350 (-0.1313, 0.6012)</t>
+          <t>0.2350
+ (-0.1313, 0.6012)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -22159,7 +22414,8 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-0.0121 (-0.0200, -0.0043)</t>
+          <t>-0.0121
+ (-0.0200, -0.0043)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -22169,7 +22425,8 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.1312 (-0.2300, 0.4924)</t>
+          <t>0.1312
+ (-0.2300, 0.4924)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -22179,7 +22436,8 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>-0.0042 (-0.0121, 0.0036)</t>
+          <t>-0.0042
+ (-0.0121, 0.0036)</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
